--- a/GAME_AUDIT.xlsx
+++ b/GAME_AUDIT.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'抜け漏れ・流れた話'!$A$1:$H$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'デバッグ・仕様疑義'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'デバッグ・仕様疑義'!$A$1:$G$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +39,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +81,11 @@
         <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -94,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -117,6 +122,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -497,9 +505,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -528,9 +534,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -2736,7 +2740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2745,6 +2749,7 @@
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2778,6 +2783,11 @@
           <t>詳細/なぜ問題か</t>
         </is>
       </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>対応(v0.25.1337)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -2808,6 +2818,11 @@
           <t>共通ヘルパーaddMeleeFinishComboが窓延長ボーナスを加算せず素の7000msを設定。カウンター/反射/ダンス経由のコンボだけスキルが黙って弱くなる(3箇所のインライン実装とは不一致)</t>
         </is>
       </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>修正済み</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -2838,6 +2853,11 @@
           <t>関所中に在庫/リフラクトリで延期された配役が、フェーズ遷移でクリアされず次の緩・ボス中に投入される=憲法第5条「緩を荒らさない」違反。緩中の突然のパンプキンの一因の可能性</t>
         </is>
       </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>修正済み</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -2868,6 +2888,11 @@
           <t>gate①はmaxRung3=天井0.49だが配役解禁は0.50から。どのゾーンでも0.50に届かず「育ち確認の関所」が看板倒れ。台本設定の自己矛盾</t>
         </is>
       </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>修正済み(関所①featured→plant)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -2898,6 +2923,11 @@
           <t>設計書ではdebt緩和はPUMPKIN_PAIR_SPAWN_EASEの一般化(置き換え)だが、実装は両方乗算(1.3×1.2≈1.56)。同じ意図を二重カウント</t>
         </is>
       </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>修正済み(max合成)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -2928,6 +2958,11 @@
           <t>緩フェーズ中の被弾が次の関所の初フレームで偽の被弾インパルス(-0.15)を発火し得る。関所開始時はpressure≈0なので実害は小</t>
         </is>
       </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>修正済み</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -2958,6 +2993,11 @@
           <t>ラン開始時の成績が仮値0.7のため「成績普通以上+犬未経験」で講習が選出され、静かな導入(relief-sparse)が消える。開始90秒グレースの前提とも衝突。導入は純休憩固定にすべきか要判断</t>
         </is>
       </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>修正済み(導入=純休憩固定)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -2988,6 +3028,11 @@
           <t>時間発火の死神は初心者ゾーン居残りランも強制終了させる(実機確認③の死因がまさにこれ)。仕様としてこれでいいか要確認</t>
         </is>
       </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>現状維持(社長指示・青線)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -3018,6 +3063,11 @@
           <t>エリア3の天井0.94&lt;0.95。関所でghostが出るのは深層域のみ(通常プールからは緩で出る)。意図した制限か確認</t>
         </is>
       </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>仕様どおり(旧段設計)と明記</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -3048,6 +3098,11 @@
           <t>実際はHP・速度・XPのみ×2。コメントと実装が不一致。またエリア係数との乗算重ねの総和も要確認</t>
         </is>
       </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>現状維持(社長指示・青線)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -3078,6 +3133,11 @@
           <t>firePhillShotはfireRateMultだけ適用しdamageMult/スキル倍率を無視。速くなるが強くならない非対称。意図か?</t>
         </is>
       </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>修正済み</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -3108,6 +3168,11 @@
           <t>ヘッダコメントが古い。調整時の誤読リスク</t>
         </is>
       </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>コメント修正</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -3138,6 +3203,11 @@
           <t>コメント齟齬</t>
         </is>
       </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>現状維持(社長指示・青線)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -3168,9 +3238,14 @@
           <t>注釈の参照値がドリフト。意図した130msなら注釈修正</t>
         </is>
       </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>注釈修正</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:G14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GAME_AUDIT.xlsx
+++ b/GAME_AUDIT.xlsx
@@ -505,7 +505,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -534,7 +533,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -1267,9 +1265,9 @@
           <t>DEVELOPMENT_LOG.md</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>対応済み(v0.25.1338)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1282,9 +1280,9 @@
           <t>中</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>意図か不具合か社長回答待ちのまま</t>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>社長承認: プレイヤー直接のクリ(銃/近接/刀/カウンター)は全て完全気絶カウントに乗る。サブウェポン自動攻撃は対象外</t>
         </is>
       </c>
     </row>

--- a/GAME_AUDIT.xlsx
+++ b/GAME_AUDIT.xlsx
@@ -12,8 +12,8 @@
     <sheet name="デバッグ・仕様疑義" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'抜け漏れ・流れた話'!$A$1:$H$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'デバッグ・仕様疑義'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'抜け漏れ・流れた話'!$A$1:$H$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'デバッグ・仕様疑義'!$A$1:$G$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -537,6 +537,37 @@
       <c r="A8" t="inlineStr">
         <is>
           <t>対応の進め方: このファイルで採否を決め、決定分をPACING_REDESIGN.md等の設計書に落としてSonnetへ。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【更新 v0.25.1347】</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>・シート2: 全13件処置済み(修正10/現状維持=青線3)。監査後に発覚した新規バグ3件(#14-16)を追記——すべて修正済み(v0.25.1343)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>・シート1: ゴールドシンク=叩き台提出済み(採否待ち)/バッチ5=実装済み/#17裏ボスクリ気絶=対応済み/ダンスB方式を追加(Sonnet実装待ち)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>・再発防止: 憲法テスト(src/utils/constitution.test.ts・7不変条件をCIで機械検査)+CLAUDE.md「実装精度の規律」(v0.25.1344)。</t>
         </is>
       </c>
     </row>
@@ -551,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -625,9 +656,9 @@
           <t>CORE_LOOP.md §6 / campaign.ts:599</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>価格未設定(叩き台提出済み)</t>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>叩き台提出済み・社長採否待ち</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -640,9 +671,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>GACHA_PULL_COST=0のテスト状態。価格案: ガチャ100g/サブ200-400g</t>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>CORE_LOOP.md§6: ガチャ100g/サブ恒久解禁200-400g(v0.25.1334)。採否が下りればSonnet実装へ</t>
         </is>
       </c>
     </row>
@@ -680,9 +711,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>現状ラン内限定。GOLD恒久解禁と接続する仕様案あり</t>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>叩き台の接続仕様に包含(恒久解禁サブのみロードアウト+商人に並ぶ)。シンク採否とセットで実装</t>
         </is>
       </c>
     </row>
@@ -745,9 +776,9 @@
           <t>PACING_REDESIGN.md §バッチ5</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>未実装</t>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>実装済み(v0.25.1340)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -760,9 +791,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>緩明けに関所の主題を選ぶメニュー。セットピース見せ場の再編入先</t>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>+実装の穴3件(苦戦誤認/回収の床/mix未指定)をv0.25.1343で修正。実機確認待ち</t>
         </is>
       </c>
     </row>
@@ -2726,8 +2757,48 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>演出</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>ダンス曲↔サークル同期の廃止→B方式(ビートがリングに合わせに来る)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>HANDOFF_DANCE_AUDIO.md末尾(v0.25.1339)</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>社長決定済み・Sonnet実装待ち</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>曲同期は構造的に解決不能と診断。メトロノーム=SFX経路のWebAudio予約。?beat=0で復帰</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H54"/>
+  <autoFilter ref="A1:H55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2738,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3242,8 +3313,113 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>フェーズ別キル集計のエイリアシング(開始時点を生参照で保存→差分常時0→全featured型を苦戦と誤認)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>killTelemetryState.ts / useGameLoop.ts</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>監査後のバッチ4実装で混入。回収演目が関所のたびに発動する根になっていた</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>修正済み(v0.25.1343・snapshot化)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>回収演目のfeaturedFloor+主役無制限で初心者ゾーンに問題児が逆流</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>reliefProgram.ts / useGameLoop.ts</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>バッチ1.5で閉じた床の裏口が回収経由で再開通。苦戦判定を「出現3体以上なのにキル2未満」へ+主役2体上限</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>修正済み(v0.25.1343)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>バグ</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>バッチ5台本(判断/三択/不意打ち)とgate-chaosのmix未指定→関所中ゾンビ配合が不発</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>gateProgram.ts / difficultyDirector.ts</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>素のエリア重みはゾンビ過多。全指定+「mix未指定シーン禁止」の回帰ガードを追加</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>修正済み(v0.25.1343)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>